--- a/out/LSTM-mamba2_repeat_1_000008.xlsx
+++ b/out/LSTM-mamba2_repeat_1_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.3</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.3</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.901262215535431</v>
+        <v>-0.3</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.284771430573892e-05</v>
+        <v>-9.315708769287449e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08368803204408806</v>
+        <v>-0.1070196012911481</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.0839103129605567</v>
+        <v>-0.107195290178011</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.5373277629695504</v>
+        <v>0.2967655539730406</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.9917769019597145</v>
+        <v>0.4869056184988809</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03828445371016911</v>
+        <v>0.0211444468266281</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5301561870355634</v>
+        <v>0.2319529869918532</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06713788748594411</v>
+        <v>0.03708028369412986</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6261349156285292</v>
+        <v>0.2849619779636297</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.08156460437383181</v>
+        <v>0.04504816554161525</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7221202161695606</v>
+        <v>0.3379744971440681</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.021584037934572</v>
+        <v>0.0119208732929875</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.683619257273359</v>
+        <v>0.3167105636086252</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01199209384279942</v>
+        <v>0.00662071862793783</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6859976516673369</v>
+        <v>0.3180218968864733</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02519383426704898</v>
+        <v>0.01391396089809551</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7244110943948437</v>
+        <v>0.3392374891218566</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009895526878771016</v>
+        <v>0.005462997413779955</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7189849255838997</v>
+        <v>0.336238264329596</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.007046534832588623</v>
+        <v>0.003889903535221407</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7231771315596153</v>
+        <v>0.3385515840686287</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002770529610440396</v>
+        <v>0.001528059163496676</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7216661678847459</v>
+        <v>0.337714767537842</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001570324256683677</v>
+        <v>0.0008643570261933406</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7220346694648515</v>
+        <v>0.3379160715260736</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005951026768783598</v>
+        <v>0.0003261721230522456</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7216532912170101</v>
+        <v>0.3377029962801158</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002757449130711239</v>
+        <v>0.0001502354225216803</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7216103532089926</v>
+        <v>0.3376769859358545</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>9.833763767730872e-05</v>
+        <v>5.232009589913218e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.721529946182443</v>
+        <v>0.3376301586008151</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.552708810617614e-05</v>
+        <v>1.169450130806508e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7214825642627725</v>
+        <v>0.3376016502520689</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>1.026354405308807e-05</v>
+        <v>3.58574352986204e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7214775404342273</v>
+        <v>0.3375966368485123</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>3.21904232466842e-06</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.721473703766122</v>
+        <v>0.337592291222703</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>5.776969076452056e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7214716355716183</v>
+        <v>0.3375889408679101</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7214660439116101</v>
+        <v>0.3375835715409224</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7214597199176022</v>
+        <v>0.3375775788074921</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7214543521290238</v>
+        <v>0.3375722110189137</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7214543888775155</v>
+        <v>0.3375722477674054</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.721454499122991</v>
+        <v>0.3375723580128809</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7214545726199746</v>
+        <v>0.3375724315098645</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7214547563624337</v>
+        <v>0.3375726152523237</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7214562997990902</v>
+        <v>0.3375741586889802</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7214577697387633</v>
+        <v>0.3375756286286533</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7214590191874853</v>
+        <v>0.3375768780773752</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7214603788816827</v>
+        <v>0.3375782377715725</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7214581739721734</v>
+        <v>0.3375760328620633</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7214577697387633</v>
+        <v>0.3375756286286533</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7214569245234513</v>
+        <v>0.3375747834133413</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7214574757508286</v>
+        <v>0.3375753346407185</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7214571450144023</v>
+        <v>0.3375750039042921</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7214568510264677</v>
+        <v>0.3375747099163576</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7214569245234513</v>
+        <v>0.3375747834133413</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7214564835415495</v>
+        <v>0.3375743424314393</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7214563732960738</v>
+        <v>0.3375742321859638</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7214563365475821</v>
+        <v>0.3375741954374721</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7214564835415495</v>
+        <v>0.3375743424314393</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7214560058111558</v>
+        <v>0.3375738647010457</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.721456961271943</v>
+        <v>0.337574820161833</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7214569245234513</v>
+        <v>0.3375747834133413</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.721456593787025</v>
+        <v>0.3375744526769149</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7214570347689269</v>
+        <v>0.3375748936588168</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7214564100445658</v>
+        <v>0.3375742689344557</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7214562263021066</v>
+        <v>0.3375740851919966</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7214558220686966</v>
+        <v>0.3375736809585865</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7214549768533847</v>
+        <v>0.3375728357432745</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.721454940104893</v>
+        <v>0.3375727989947828</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7214550870988602</v>
+        <v>0.3375729459887501</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7214550136018766</v>
+        <v>0.3375728724917665</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7214550870988602</v>
+        <v>0.3375729459887501</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7214551238473521</v>
+        <v>0.337572982737242</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7214550136018766</v>
+        <v>0.3375728724917665</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7214554545837785</v>
+        <v>0.3375733134736684</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7214553443383029</v>
+        <v>0.3375732032281928</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.721455307589811</v>
+        <v>0.3375731664797009</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7214552340928274</v>
+        <v>0.3375730929827173</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7214551973443357</v>
+        <v>0.3375730562342256</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7214549768533847</v>
+        <v>0.3375728357432745</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7214549033564011</v>
+        <v>0.3375727622462909</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7214548298594174</v>
+        <v>0.3375726887493073</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7214548666079094</v>
+        <v>0.3375727254977992</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7214547563624337</v>
+        <v>0.3375726152523237</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7214548666079094</v>
+        <v>0.3375727254977992</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7214551605958438</v>
+        <v>0.3375730194857337</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_1_000008.xlsx
+++ b/out/LSTM-mamba2_repeat_1_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.901262215535431</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.901262215535431</v>
+        <v>0.7627717100636435</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.7627717100636433</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.901262215535431</v>
+        <v>0.7627717100636433</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.50126221553543</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.901262215535431</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.901262215535431</v>
+        <v>1.469436947795724</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.901262215535431</v>
+        <v>0.7627717100636435</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.284771430573892e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08368803204408806</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-8.500900750700385e-05</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>-0.3002337449325959</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.3003187539401029</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.3003187539401029</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.3003187539401029</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.3003187539401029</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.3003187539401029</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.3003187539401029</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.3003187539401029</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.3003187539401029</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.3003187539401029</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.3003187539401029</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.3003187539401029</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.08376087975839375</v>
+        <v>-0.3003187539401029</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.0839103129605567</v>
+        <v>-0.3004057143967445</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.5373277629695504</v>
+        <v>0.3126899976558283</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.9917769019597145</v>
+        <v>0.3255746571607269</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03828445371016911</v>
+        <v>0.02227906009559548</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.4505587654005176</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5301561870355634</v>
+        <v>0.05694126395328855</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06713788748594411</v>
+        <v>0.0390700087812024</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6261349156285292</v>
+        <v>0.1127947131834477</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.08156460437383181</v>
+        <v>0.04746513475120664</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7221202161695606</v>
+        <v>0.1686518805213135</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.021584037934572</v>
+        <v>0.01256046390348581</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.683619257273359</v>
+        <v>0.1462467791796117</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01199209384279942</v>
+        <v>0.006976585021575686</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6859976516673369</v>
+        <v>0.1476287738060595</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02519383426704898</v>
+        <v>0.0146615462840951</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7244110943948437</v>
+        <v>0.1699828818834552</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009895526878771016</v>
+        <v>0.005756077230864063</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7189849255838997</v>
+        <v>0.1668231870221994</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.007046534832588623</v>
+        <v>0.004098620686577381</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7231771315596153</v>
+        <v>0.169260739129887</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002770529610440396</v>
+        <v>0.001609532635427412</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7216661678847459</v>
+        <v>0.1683793487440788</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001570324256683677</v>
+        <v>0.0009121408343706341</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7220346694648515</v>
+        <v>0.1685917982941403</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005951026768783598</v>
+        <v>0.0003437876615124714</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7216532912170101</v>
+        <v>0.1683676747630206</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002757449130711239</v>
+        <v>0.0001590431060690097</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7216103532089926</v>
+        <v>0.1683405500095145</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>9.833763767730872e-05</v>
+        <v>5.47420717821941e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.721529946182443</v>
+        <v>0.1682916613343558</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.552708810617614e-05</v>
+        <v>1.264847281138308e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7214825642627725</v>
+        <v>0.1682618285506198</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>1.026354405308807e-05</v>
+        <v>4.062729281521043e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7214775404342273</v>
+        <v>0.168256814402421</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>3.21904232466842e-06</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.721473703766122</v>
+        <v>0.1682525055251035</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>5.776969076452056e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7214716355716183</v>
+        <v>0.1682493379035387</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7214660439116101</v>
+        <v>0.1682439685765509</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7214597199176022</v>
+        <v>0.1682379758431206</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7214543521290238</v>
+        <v>0.1682326080545422</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7214543888775155</v>
+        <v>0.1682326448030339</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.721454499122991</v>
+        <v>0.1682327550485095</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7214545726199746</v>
+        <v>0.1682328285454931</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7214547563624337</v>
+        <v>0.1682330122879522</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7214562997990902</v>
+        <v>0.1682345557246087</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7214577697387633</v>
+        <v>0.1682360256642818</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7214590191874853</v>
+        <v>0.1682372751130038</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636436</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7214603788816827</v>
+        <v>0.1682386348072011</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7214581739721734</v>
+        <v>0.1682364298976918</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7214577697387633</v>
+        <v>0.1682360256642818</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7214569245234513</v>
+        <v>0.1682351804489698</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7214574757508286</v>
+        <v>0.1682357316763471</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7214571450144023</v>
+        <v>0.1682354009399207</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7214568510264677</v>
+        <v>0.1682351069519862</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7214569245234513</v>
+        <v>0.1682351804489698</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7214564835415495</v>
+        <v>0.1682347394670679</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7214563732960738</v>
+        <v>0.1682346292215923</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7214563365475821</v>
+        <v>0.1682345924731006</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7214564835415495</v>
+        <v>0.1682347394670679</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7214560058111558</v>
+        <v>0.1682342617366742</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.721456961271943</v>
+        <v>0.1682352171974615</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7214569245234513</v>
+        <v>0.1682351804489698</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.721456593787025</v>
+        <v>0.1682348497125434</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7214570347689269</v>
+        <v>0.1682352906944454</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7214564100445658</v>
+        <v>0.1682346659700843</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7214562263021066</v>
+        <v>0.1682344822276251</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7214558220686966</v>
+        <v>0.1682340779942151</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7214549768533847</v>
+        <v>0.1682332327789031</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.721454940104893</v>
+        <v>0.1682331960304114</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7214550870988602</v>
+        <v>0.1682333430243786</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7214550136018766</v>
+        <v>0.168233269527395</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7214550870988602</v>
+        <v>0.1682333430243786</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7214551238473521</v>
+        <v>0.1682333797728706</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7214550136018766</v>
+        <v>0.168233269527395</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7214554545837785</v>
+        <v>0.168233710509297</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7214553443383029</v>
+        <v>0.1682336002638214</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.721455307589811</v>
+        <v>0.1682335635153295</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7214552340928274</v>
+        <v>0.1682334900183459</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7214551973443357</v>
+        <v>0.1682334532698542</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7214549768533847</v>
+        <v>0.1682332327789031</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7214549033564011</v>
+        <v>0.1682331592819195</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7214548298594174</v>
+        <v>0.1682330857849359</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7214548666079094</v>
+        <v>0.1682331225334278</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7214547563624337</v>
+        <v>0.1682330122879522</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7214548666079094</v>
+        <v>0.1682331225334278</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7214551605958438</v>
+        <v>0.1682334165213623</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_1_000008.xlsx
+++ b/out/LSTM-mamba2_repeat_1_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.2811776399612427</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.1522895991802216</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.046389140188694</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.03908324241638184</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.01642698794603348</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.16</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.002206616103649139</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-5.973875522613525e-05</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.003468677401542664</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.01172167807817459</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.01049040257930756</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.003269799053668976</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.005380455404520035</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.256106472331563</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.003117479383945465</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.005032520741224289</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.008923955261707306</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.256106472331563</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.002643804997205734</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.256106472331563</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.01146161928772926</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01425591856241226</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.015480637550354</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01646658405661583</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01181108132004738</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.01428234204649925</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.01434490457177162</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.669436947795724</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01635038480162621</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.669436947795724</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.01184409484267235</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.669436947795724</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0191049799323082</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.669436947795724</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.02004425227642059</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.469436947795724</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.02081653848290443</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.469436947795724</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01872001588344574</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.469436947795724</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01828884705901146</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.7627717100636435</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.002024687826633453</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.7627717100636433</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.007511042058467865</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.7627717100636433</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.02455681562423706</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.469436947795724</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.02917611226439476</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.469436947795724</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.02336755767464638</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.02370022609829903</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.669436947795724</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0205550380051136</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.669436947795724</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.02052177861332893</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.669436947795724</v>
+        <v>-0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01767892763018608</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.669436947795724</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.004946131259202957</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.669436947795724</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01349208131432533</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.669436947795724</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.008389830589294434</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.469436947795724</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.004025883972644806</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7627717100636435</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.01357416901737452</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>-7.719068296707701e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.08867726889193431</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.02138431556522846</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>-8.500900750700385e-05</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>-0.3002337449325959</v>
+        <v>0</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.0105542466044426</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.3003187539401029</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01621908321976662</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.3003187539401029</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01532347314059734</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.3003187539401029</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.02239162661135197</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.3003187539401029</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01595775410532951</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.3003187539401029</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01918707974255085</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.3003187539401029</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.01229657046496868</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.3003187539401029</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.01009340398013592</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.3003187539401029</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.004423718899488449</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.3003187539401029</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.002866259776055813</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.3003187539401029</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.0005680043250322342</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.3003187539401029</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.001898337155580521</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.9627717100636434</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.3003187539401029</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.002606943249702454</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9627717100636434</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.3004057143967445</v>
+        <v>-0.0888428258004114</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3126899976558283</v>
+        <v>0.3177448223563752</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01156589854508638</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3255746571607269</v>
+        <v>0.5472569006066802</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02227906009559548</v>
+        <v>0.02263921529421907</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.007254548370838165</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4505587654005176</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.05694126395328855</v>
+        <v>0.2742808846022973</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0390700087812024</v>
+        <v>0.03970159828710793</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.004513900727033615</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1127947131834477</v>
+        <v>0.331037237453491</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04746513475120664</v>
+        <v>0.04823275319728687</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01436132378876209</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.1686518805213135</v>
+        <v>0.3877973679328209</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01256046390348581</v>
+        <v>0.01276342996409287</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01137165352702141</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1462467791796117</v>
+        <v>0.3650302245899483</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.006976585021575686</v>
+        <v>0.007089214900799215</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.006048766896128654</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.1476287738060595</v>
+        <v>0.3664346315481942</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0146615462840951</v>
+        <v>0.01489892391181456</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.02005456015467644</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.1699828818834552</v>
+        <v>0.3891506211436058</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.005756077230864063</v>
+        <v>0.00584932989993628</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01840086653828621</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1668231870221994</v>
+        <v>0.3859398676240335</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004098620686577381</v>
+        <v>0.004164168221713969</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.03337357938289642</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.169260739129887</v>
+        <v>0.3884169493346468</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001609532635427412</v>
+        <v>0.001636690459404324</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.03954385966062546</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1683793487440788</v>
+        <v>0.3875211909770556</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0009121408343706341</v>
+        <v>0.0009260135528737193</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.05091104656457901</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1685917982941403</v>
+        <v>0.3877371134224343</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003437876615124714</v>
+        <v>0.00034965950766588</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.05744997039437294</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1683676747630206</v>
+        <v>0.387509307129594</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001590431060690097</v>
+        <v>0.000161245026955842</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.06190814822912216</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1683405500095145</v>
+        <v>0.3874818119025473</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.47420717821941e-05</v>
+        <v>5.635672237090206e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.06542851030826569</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1682916613343558</v>
+        <v>0.3874320389805334</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.264847281138308e-05</v>
+        <v>1.312545856304208e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.05494403839111328</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1682618285506198</v>
+        <v>0.3874018747157289</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.03611572459340096</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.168256814402421</v>
+        <v>0.3873968605675301</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01955350115895271</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1682525055251035</v>
+        <v>0.3873925516902127</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.009016342461109161</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.1682493379035387</v>
+        <v>0.3873893840686479</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01817974448204041</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1682439685765509</v>
+        <v>0.3873840147416601</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.01934122294187546</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1682379758431206</v>
+        <v>0.3873780220082297</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.01697865501046181</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1682326080545422</v>
+        <v>0.3873726542196513</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.007917813025414944</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.1682326448030339</v>
+        <v>0.387372690968143</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.00458881352096796</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.256106472331563</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1682327550485095</v>
+        <v>0.3873728012136186</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.002526009455323219</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1682328285454931</v>
+        <v>0.3873728747106022</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.02339816838502884</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1682330122879522</v>
+        <v>0.3873730584530614</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.0307006761431694</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1682345557246087</v>
+        <v>0.3873746018897178</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.06663099676370621</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1682360256642818</v>
+        <v>0.3873760718293909</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.1033095419406891</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.669436947795724</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.1682372751130038</v>
+        <v>0.3873773212781129</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.08672479540109634</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.9627717100636436</v>
+        <v>-0.16</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.1682386348072011</v>
+        <v>0.3873786809723103</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.03711959719657898</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1682364298976918</v>
+        <v>0.387376476062801</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.09417954087257385</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1682360256642818</v>
+        <v>0.3873760718293909</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.1303347647190094</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1682351804489698</v>
+        <v>0.387375226614079</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.1516838669776917</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1682357316763471</v>
+        <v>0.3873757778414562</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.1611739993095398</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.1682354009399207</v>
+        <v>0.3873754471050299</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.1515354812145233</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1682351069519862</v>
+        <v>0.3873751531170954</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.1493437886238098</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1682351804489698</v>
+        <v>0.387375226614079</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.1357347369194031</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1682347394670679</v>
+        <v>0.387374785632177</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.1164842694997787</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.1682346292215923</v>
+        <v>0.3873746753867015</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.09283491224050522</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.1682345924731006</v>
+        <v>0.3873746386382098</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.08722515404224396</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1682347394670679</v>
+        <v>0.387374785632177</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.0579061359167099</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1682342617366742</v>
+        <v>0.3873743079017834</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.03829200565814972</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1682352171974615</v>
+        <v>0.3873752633625707</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.06043737381696701</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1682351804489698</v>
+        <v>0.387375226614079</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.07553911954164505</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.1682348497125434</v>
+        <v>0.3873748958776526</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.08825724571943283</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1682352906944454</v>
+        <v>0.3873753368595545</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.1021205335855484</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1682346659700843</v>
+        <v>0.3873747121351934</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.1067801490426064</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.1682344822276251</v>
+        <v>0.3873745283927342</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.1161036044359207</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.1682340779942151</v>
+        <v>0.3873741241593242</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.1108534336090088</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1682332327789031</v>
+        <v>0.3873732789440122</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.08301521092653275</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1682331960304114</v>
+        <v>0.3873732421955206</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.06105245277285576</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1682333430243786</v>
+        <v>0.3873733891894878</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.04224146157503128</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.168233269527395</v>
+        <v>0.3873733156925042</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.03735709190368652</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1682333430243786</v>
+        <v>0.3873733891894878</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.03213087096810341</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1682333797728706</v>
+        <v>0.3873734259379797</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.0189446322619915</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.168233269527395</v>
+        <v>0.3873733156925042</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.01952964067459106</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.168233710509297</v>
+        <v>0.3873737566744061</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.02094096317887306</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1682336002638214</v>
+        <v>0.3873736464289306</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.02047472447156906</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1682335635153295</v>
+        <v>0.3873736096804387</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.02294664457440376</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1682334900183459</v>
+        <v>0.387373536183455</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.02640881389379501</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1682334532698542</v>
+        <v>0.3873734994349634</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.02643792331218719</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1682332327789031</v>
+        <v>0.3873732789440122</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.02732160314917564</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1682331592819195</v>
+        <v>0.3873732054470286</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.01776133105158806</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1682330857849359</v>
+        <v>0.387373131950045</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01772745326161385</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1682331225334278</v>
+        <v>0.3873731686985369</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.01077129319310188</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1682330122879522</v>
+        <v>0.3873730584530614</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.007065538316965103</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1682331225334278</v>
+        <v>0.3873731686985369</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003922730684280396</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1682334165213623</v>
+        <v>0.3873734626864714</v>
       </c>
     </row>
   </sheetData>
